--- a/r5-TC-FHIR-AG-Scheduling-R5-5-add-fsh-profiles-and-value-set-service-type/StructureDefinition-at-scheduling-schedule.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-5-add-fsh-profiles-and-value-set-service-type/StructureDefinition-at-scheduling-schedule.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="200">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T10:12:02+00:00</t>
+    <t>2025-01-28T14:00:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -541,7 +541,10 @@
     <t>The specific service that is to be performed during this appointment.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type</t>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/ValueSet/AtSchedulingServiceType</t>
   </si>
   <si>
     <t>n/a</t>
@@ -584,7 +587,7 @@
     <t>Schedule.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|CareTeam|RelatedPerson|Device|HealthcareService|Location)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-patient|http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-practitionerRole|CareTeam|RelatedPerson|Device|http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-healthcareservice|Location)
 </t>
   </si>
   <si>
@@ -942,7 +945,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="101.45703125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -957,7 +960,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="73.81640625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="43.80859375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="76.62890625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -2478,11 +2481,11 @@
         <v>18</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>18</v>
@@ -2521,15 +2524,15 @@
         <v>18</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2555,10 +2558,10 @@
         <v>158</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2585,13 +2588,13 @@
         <v>18</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>18</v>
@@ -2609,7 +2612,7 @@
         <v>18</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -2635,10 +2638,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2661,16 +2664,16 @@
         <v>86</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -2720,7 +2723,7 @@
         <v>18</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
@@ -2746,10 +2749,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2772,16 +2775,16 @@
         <v>86</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2831,7 +2834,7 @@
         <v>18</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>85</v>
@@ -2846,21 +2849,21 @@
         <v>97</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2883,13 +2886,13 @@
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2940,7 +2943,7 @@
         <v>18</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -2955,21 +2958,21 @@
         <v>97</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2992,13 +2995,13 @@
         <v>18</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3049,7 +3052,7 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
@@ -3070,7 +3073,7 @@
         <v>18</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
